--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A - AÇÕES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="R - REAL ESTATE (FUNDOS IMOBILI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="C - CAIXA (RENDA FIXA)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="A - ALTERNATIVOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A - AÇÕES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R - REAL ESTATE (FUNDOS IMOBILI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C - CAIXA (RENDA FIXA)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A - ALTERNATIVOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$J$38</definedName>

--- a/finclass_carteira.xlsx
+++ b/finclass_carteira.xlsx
@@ -1592,8 +1592,8 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>MS GLOBAL OPPORTUNITIES
-Internacional</t>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR
+Internacional (33.913.562/0001-85)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2703,8 +2703,8 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>MS GLOBAL OPPORTUNITIES
-Internacional</t>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR
+Internacional (33.913.562/0001-85)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
